--- a/public/Embecta-Credit-Model.xlsx
+++ b/public/Embecta-Credit-Model.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="573">
-  <si>
-    <t xml:space="preserve">EMBECTA CORP. (EMBC) — HIGH YIELD CREDIT MODEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Three-statement model, tranche-level debt schedule, base / downside / stress. Built from SEC filings only.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="575">
+  <si>
+    <t xml:space="preserve">EMBECTA CORP. (EMBC): HIGH-YIELD CREDIT MODEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three-statement model with a tranche-level debt schedule and base, downside and stress cases. Built from SEC filings.</t>
   </si>
   <si>
     <t xml:space="preserve">Analyst</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">Ratings</t>
   </si>
   <si>
-    <t xml:space="preserve">S&amp;P B / stable (cut from B+ on 11 May 2026). Moody's B3 per research brief — not yet verified at source.</t>
+    <t xml:space="preserve">S&amp;P B / stable (cut from B+ on 11 May 2026). Moody's B3 per research brief, not yet verified at source.</t>
   </si>
   <si>
     <t xml:space="preserve">Instrument analysed</t>
@@ -71,19 +71,19 @@
     <t xml:space="preserve">Recommendation</t>
   </si>
   <si>
-    <t xml:space="preserve">BUY, moderate size: 5.00% senior secured notes due Feb 2030 at ~81 (proxy price; ~12% yield to maturity).</t>
+    <t xml:space="preserve">Buy in moderate size: 5.00% senior secured notes due Feb 2030 at about 81 (proxy price, ~12.1% yield to maturity).</t>
   </si>
   <si>
     <t xml:space="preserve">Thesis (1 sentence)</t>
   </si>
   <si>
-    <t xml:space="preserve">A ~12% yield on a first-lien claim pays for a franchise in structural decline: in the downside Embecta still covers cash interest ~2.1x, stays inside its 4.75x covenant and refinances; in stress, 1L recovery of ~60-85 cents caps the loss.</t>
+    <t xml:space="preserve">In the downside the company still covers cash interest 2.1x, stays under the 4.75x covenant and refinances; in stress, first-lien recovery of about 59-85 cents limits the loss.</t>
   </si>
   <si>
     <t xml:space="preserve">Thesis breaks if</t>
   </si>
   <si>
-    <t xml:space="preserve">Gross margin runs ~1pt below the downside path (~50% by FY28 vs 56.4% in Q3 FY26), i.e. covenant EBITDA under ~$213m in FY28: the 4.75x covenant breaks and the Mar-29 term loan is no longer refinanceable on its own.</t>
+    <t xml:space="preserve">Gross margin about 1.2 points below the downside path (~50% by FY28), equal to covenant EBITDA under ~$213m in FY28.</t>
   </si>
   <si>
     <t xml:space="preserve">Data as of</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">5.00% notes yield to maturity at proxy price</t>
   </si>
   <si>
-    <t xml:space="preserve">price (proxy — replace with TRACE)</t>
+    <t xml:space="preserve">price (proxy; replace with TRACE)</t>
   </si>
   <si>
     <t xml:space="preserve">Model integrity</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">Blue text</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardcoded input — typed from a filing or an assumption on Drivers</t>
+    <t xml:space="preserve">Hardcoded input, typed from a filing or set on Drivers</t>
   </si>
   <si>
     <t xml:space="preserve">Black text</t>
   </si>
   <si>
-    <t xml:space="preserve">Formula — do not overwrite</t>
+    <t xml:space="preserve">Formula; do not overwrite</t>
   </si>
   <si>
     <t xml:space="preserve">Green text</t>
   </si>
   <si>
-    <t xml:space="preserve">Link from another tab — do not overwrite</t>
+    <t xml:space="preserve">Link from another tab; do not overwrite</t>
   </si>
   <si>
     <t xml:space="preserve">Yellow fill</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">FY27E COVENANT BREACH</t>
   </si>
   <si>
-    <t xml:space="preserve">Snapshot pasted as values after recalculating each scenario (23 Oct 2026). Column H is live for whichever scenario B3 selects.</t>
+    <t xml:space="preserve">Snapshot pasted as values after recalculating each scenario (26 Oct 2026). Column H is live for whichever scenario B3 selects.</t>
   </si>
   <si>
     <t xml:space="preserve">THESIS-BREAK SEARCH (values)</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">Leave at 0.0% for the scenarios as written. Enter e.g. -3.0% to cut gross margin by 3 points in every year from FY27 (lost manufacturing leverage beyond the scenario).</t>
   </si>
   <si>
-    <t xml:space="preserve">DRIVERS — every forecast assumption lives here</t>
+    <t xml:space="preserve">DRIVERS: all forecast assumptions</t>
   </si>
   <si>
     <t xml:space="preserve">Blue = input. Each driver: an ACTIVE row (black, picks the scenario via Scenarios!$B$3) and Base / Downside / Stress input rows. Nothing is hardcoded anywhere else.</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">Source / rationale</t>
   </si>
   <si>
-    <t xml:space="preserve">REVENUE — US pen needle franchise decomposed into drug-utilization drivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US — insulin-pen user volume growth</t>
+    <t xml:space="preserve">REVENUE: US pen needles split into volume, price and share drivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US insulin-pen user volume growth</t>
   </si>
   <si>
     <t xml:space="preserve">ACTIVE</t>
@@ -368,21 +368,27 @@
     <t xml:space="preserve">Fewer injected-insulin users and injections: GLP-1s delaying/replacing T2D basal-bolus insulin, AID pump adoption in T1D (no pen needles), and the shift to lower-cost retail channels after the IRA Part D redesign. S&amp;P (11 May 2026) cites all four. FY26 set so total revenue hits guidance midpoint.</t>
   </si>
   <si>
-    <t xml:space="preserve">   US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US — net price / customer &amp; payer mix</t>
+    <t xml:space="preserve">   US insulin-pen user volume growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US net price (customer and payer mix)</t>
   </si>
   <si>
     <t xml:space="preserve">Q3 FY26 call: customer and payer mix had a larger effect on net pricing than in Q2; ~$20m unfavorable price in Q3 alone. Part D plans now carry more of the insulin cost, so they push hard for the cheapest needle.</t>
   </si>
   <si>
-    <t xml:space="preserve">US — share change (customer wins / losses)</t>
+    <t xml:space="preserve">   US net price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US share change (customer wins and losses)</t>
   </si>
   <si>
     <t xml:space="preserve">S&amp;P: a large US retail customer moved to a lower-cost alternative and a lower-cost provider took share at another large customer. Base annualises the FY26 loss into FY27, then holds share. Downside/Stress assume further private-label erosion.</t>
   </si>
   <si>
+    <t xml:space="preserve">   US share change</t>
+  </si>
+  <si>
     <t xml:space="preserve">International (ex-Owen Mumford) growth</t>
   </si>
   <si>
@@ -431,13 +437,13 @@
     <t xml:space="preserve">   R&amp;D % of revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Other operating expense — non-recurring ($mm)</t>
+    <t xml:space="preserve">Other operating expense, non-recurring ($mm)</t>
   </si>
   <si>
     <t xml:space="preserve">9M FY26 gross $37.9m (separation $9.6m, cloud amort $7.8m, acquisition $16.9m, other $3.6m) + ~$10m Q4. Added back to Credit EBITDA but paid in cash, so FCF carries it.</t>
   </si>
   <si>
-    <t xml:space="preserve">   Other operating expense</t>
+    <t xml:space="preserve">   Other operating expense, non-recurring</t>
   </si>
   <si>
     <t xml:space="preserve">Gain on asset sales ($mm; = proceeds, zero book value)</t>
@@ -635,7 +641,7 @@
     <t xml:space="preserve">   Distressed EV / EBITDA for recovery</t>
   </si>
   <si>
-    <t xml:space="preserve">FY26 ACQUISITION — Owen Mumford purchase accounting (facts, scenario-invariant)</t>
+    <t xml:space="preserve">FY26 ACQUISITION: Owen Mumford purchase accounting (same in every scenario)</t>
   </si>
   <si>
     <t xml:space="preserve">Cash paid, net of cash acquired ($mm)</t>
@@ -704,7 +710,7 @@
     <t xml:space="preserve">FX and pension items; FY25 +$1.5m, 9M FY26 -$0.4m. Not forecast.</t>
   </si>
   <si>
-    <t xml:space="preserve">HISTORICALS — as reported ($mm)</t>
+    <t xml:space="preserve">HISTORICALS: as reported ($mm)</t>
   </si>
   <si>
     <t xml:space="preserve">Typed from 10-K and 10-Q filings (EDGAR). Blue = as reported. Black = subtotal formula. Reported totals are re-entered and tied on Checks.</t>
@@ -806,7 +812,7 @@
     <t xml:space="preserve">Re-entered from the filing; tied on Checks.</t>
   </si>
   <si>
-    <t xml:space="preserve">EBITDA BUILD — what I add back, and why</t>
+    <t xml:space="preserve">EBITDA BUILD: add-backs and the reasoning</t>
   </si>
   <si>
     <t xml:space="preserve">D&amp;A (cash flow statement)</t>
@@ -1265,19 +1271,19 @@
     <t xml:space="preserve">  of which term debt (TLB + notes + new)</t>
   </si>
   <si>
-    <t xml:space="preserve">Unamortized issuance costs — beginning</t>
+    <t xml:space="preserve">Unamortized issuance costs, beginning</t>
   </si>
   <si>
     <t xml:space="preserve">  amortization (non-cash interest)</t>
   </si>
   <si>
-    <t xml:space="preserve">Unamortized issuance costs — ending</t>
+    <t xml:space="preserve">Unamortized issuance costs, ending</t>
   </si>
   <si>
     <t xml:space="preserve">Net debt paydown in year</t>
   </si>
   <si>
-    <t xml:space="preserve">Interest — on BEGINNING balances (no circularity)</t>
+    <t xml:space="preserve">Interest on opening balances (no circular references)</t>
   </si>
   <si>
     <t xml:space="preserve">SOFR</t>
@@ -1595,13 +1601,13 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">SUMMARY — active scenario (feeds the Scenarios snapshot and the Cover)</t>
+    <t xml:space="preserve">SUMMARY for the active scenario (feeds the Scenarios snapshot and the Cover)</t>
   </si>
   <si>
     <t xml:space="preserve">Instrument: 5.00% senior secured notes due 15 Feb 2030</t>
   </si>
   <si>
-    <t xml:space="preserve">Price (cents) — proxy</t>
+    <t xml:space="preserve">Price (cents), proxy</t>
   </si>
   <si>
     <t xml:space="preserve">Proxy: blended Level 2 fair value / carrying at 30 Jun 26 = 81.5 (10-Q). Cbonds shows the 6.75% 2030s at G+~930bp (~13% yield), which would put the 5s nearer 78. Replace with the TRACE print.</t>
@@ -1625,7 +1631,7 @@
     <t xml:space="preserve">Points of cushion (+) or loss (-) if the issuer defaulted at the trough and the 1L recovered at the distressed multiple.</t>
   </si>
   <si>
-    <t xml:space="preserve">Maturity wall — principal due by fiscal year ($mm)</t>
+    <t xml:space="preserve">Maturity wall: principal due by fiscal year ($mm)</t>
   </si>
   <si>
     <t xml:space="preserve">FY2026</t>
@@ -1655,7 +1661,7 @@
     <t xml:space="preserve">Thresholds that matter: interest coverage below 2.0x; covenant-proxy net leverage above 4.75x; and whether the Mar-29 term loan and Feb-30 notes can be refinanced from a FY28 balance sheet.</t>
   </si>
   <si>
-    <t xml:space="preserve">CHECKS — every status must read OK</t>
+    <t xml:space="preserve">CHECKS: every status should read OK</t>
   </si>
   <si>
     <t xml:space="preserve">Check</t>
@@ -2500,11 +2506,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="67714492"/>
-        <c:axId val="36645163"/>
+        <c:axId val="12979173"/>
+        <c:axId val="88556320"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="67714492"/>
+        <c:axId val="12979173"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2536,7 +2542,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36645163"/>
+        <c:crossAx val="88556320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2544,7 +2550,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36645163"/>
+        <c:axId val="88556320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2620,7 +2626,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67714492"/>
+        <c:crossAx val="12979173"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3938,7 +3944,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>23</v>
@@ -3961,7 +3967,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>24</v>
@@ -3984,7 +3990,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>25</v>
@@ -4007,7 +4013,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>111</v>
@@ -4033,12 +4039,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>23</v>
@@ -4061,7 +4067,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>24</v>
@@ -4084,7 +4090,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>25</v>
@@ -4107,7 +4113,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>111</v>
@@ -4133,12 +4139,12 @@
         <v>0.025</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>23</v>
@@ -4161,7 +4167,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>24</v>
@@ -4184,7 +4190,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>25</v>
@@ -4207,7 +4213,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>111</v>
@@ -4233,12 +4239,12 @@
         <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>23</v>
@@ -4261,7 +4267,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>24</v>
@@ -4284,7 +4290,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>25</v>
@@ -4307,7 +4313,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="24" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -4319,7 +4325,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>111</v>
@@ -4345,12 +4351,12 @@
         <v>0.54</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>23</v>
@@ -4373,7 +4379,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>24</v>
@@ -4396,7 +4402,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>25</v>
@@ -4419,7 +4425,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>111</v>
@@ -4445,12 +4451,12 @@
         <v>0.29</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>23</v>
@@ -4473,7 +4479,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>24</v>
@@ -4496,7 +4502,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>25</v>
@@ -4519,7 +4525,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>111</v>
@@ -4545,12 +4551,12 @@
         <v>0.022</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>23</v>
@@ -4573,7 +4579,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>24</v>
@@ -4596,7 +4602,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>25</v>
@@ -4619,7 +4625,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>111</v>
@@ -4645,12 +4651,12 @@
         <v>5</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>23</v>
@@ -4673,7 +4679,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B49" s="15" t="s">
         <v>24</v>
@@ -4696,7 +4702,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B50" s="15" t="s">
         <v>25</v>
@@ -4719,7 +4725,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>111</v>
@@ -4745,12 +4751,12 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B53" s="15" t="s">
         <v>23</v>
@@ -4773,7 +4779,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B54" s="15" t="s">
         <v>24</v>
@@ -4796,7 +4802,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B55" s="15" t="s">
         <v>25</v>
@@ -4819,7 +4825,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>111</v>
@@ -4845,12 +4851,12 @@
         <v>0.042</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B58" s="15" t="s">
         <v>23</v>
@@ -4873,7 +4879,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B59" s="15" t="s">
         <v>24</v>
@@ -4896,7 +4902,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B60" s="15" t="s">
         <v>25</v>
@@ -4919,7 +4925,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>111</v>
@@ -4945,12 +4951,12 @@
         <v>4.5</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B63" s="15" t="s">
         <v>23</v>
@@ -4973,7 +4979,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B64" s="15" t="s">
         <v>24</v>
@@ -4996,7 +5002,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B65" s="15" t="s">
         <v>25</v>
@@ -5019,7 +5025,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>111</v>
@@ -5045,12 +5051,12 @@
         <v>0.02</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B68" s="15" t="s">
         <v>23</v>
@@ -5073,7 +5079,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B69" s="15" t="s">
         <v>24</v>
@@ -5096,7 +5102,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B70" s="15" t="s">
         <v>25</v>
@@ -5119,7 +5125,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>111</v>
@@ -5145,12 +5151,12 @@
         <v>0.025</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B73" s="15" t="s">
         <v>23</v>
@@ -5173,7 +5179,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B74" s="15" t="s">
         <v>24</v>
@@ -5196,7 +5202,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B75" s="15" t="s">
         <v>25</v>
@@ -5219,7 +5225,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>111</v>
@@ -5245,12 +5251,12 @@
         <v>0.27</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B78" s="15" t="s">
         <v>23</v>
@@ -5273,7 +5279,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B79" s="15" t="s">
         <v>24</v>
@@ -5296,7 +5302,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B80" s="15" t="s">
         <v>25</v>
@@ -5319,7 +5325,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B82" s="25"/>
       <c r="C82" s="25"/>
@@ -5331,7 +5337,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>111</v>
@@ -5357,12 +5363,12 @@
         <v>62</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B84" s="15" t="s">
         <v>23</v>
@@ -5385,7 +5391,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B85" s="15" t="s">
         <v>24</v>
@@ -5408,7 +5414,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B86" s="15" t="s">
         <v>25</v>
@@ -5431,7 +5437,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>111</v>
@@ -5457,12 +5463,12 @@
         <v>180</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>23</v>
@@ -5485,7 +5491,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B90" s="15" t="s">
         <v>24</v>
@@ -5508,7 +5514,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B91" s="15" t="s">
         <v>25</v>
@@ -5531,7 +5537,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>111</v>
@@ -5557,12 +5563,12 @@
         <v>72</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B94" s="15" t="s">
         <v>23</v>
@@ -5585,7 +5591,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B95" s="15" t="s">
         <v>24</v>
@@ -5608,7 +5614,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B96" s="15" t="s">
         <v>25</v>
@@ -5631,7 +5637,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B98" s="25"/>
       <c r="C98" s="25"/>
@@ -5643,7 +5649,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>111</v>
@@ -5669,12 +5675,12 @@
         <v>2.3</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B100" s="15" t="s">
         <v>23</v>
@@ -5697,7 +5703,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B101" s="15" t="s">
         <v>24</v>
@@ -5720,7 +5726,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B102" s="15" t="s">
         <v>25</v>
@@ -5743,7 +5749,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>111</v>
@@ -5769,12 +5775,12 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B105" s="15" t="s">
         <v>23</v>
@@ -5797,7 +5803,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B106" s="15" t="s">
         <v>24</v>
@@ -5820,7 +5826,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B107" s="15" t="s">
         <v>25</v>
@@ -5843,7 +5849,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>111</v>
@@ -5869,12 +5875,12 @@
         <v>6</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B110" s="15" t="s">
         <v>23</v>
@@ -5897,7 +5903,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B111" s="15" t="s">
         <v>24</v>
@@ -5920,7 +5926,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B112" s="15" t="s">
         <v>25</v>
@@ -5943,7 +5949,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>111</v>
@@ -5969,12 +5975,12 @@
         <v>200</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B115" s="15" t="s">
         <v>23</v>
@@ -5997,7 +6003,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B116" s="15" t="s">
         <v>24</v>
@@ -6020,7 +6026,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B117" s="15" t="s">
         <v>25</v>
@@ -6043,7 +6049,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>111</v>
@@ -6069,12 +6075,12 @@
         <v>1</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B120" s="15" t="s">
         <v>23</v>
@@ -6097,7 +6103,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B121" s="15" t="s">
         <v>24</v>
@@ -6120,7 +6126,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B122" s="15" t="s">
         <v>25</v>
@@ -6143,7 +6149,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>111</v>
@@ -6169,12 +6175,12 @@
         <v>0.0325</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B125" s="15" t="s">
         <v>23</v>
@@ -6197,7 +6203,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B126" s="15" t="s">
         <v>24</v>
@@ -6220,7 +6226,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="15" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B127" s="15" t="s">
         <v>25</v>
@@ -6243,7 +6249,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>111</v>
@@ -6269,12 +6275,12 @@
         <v>1</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B130" s="15" t="s">
         <v>23</v>
@@ -6297,7 +6303,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B131" s="15" t="s">
         <v>24</v>
@@ -6320,7 +6326,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B132" s="15" t="s">
         <v>25</v>
@@ -6343,7 +6349,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>111</v>
@@ -6369,12 +6375,12 @@
         <v>0.09</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B135" s="15" t="s">
         <v>23</v>
@@ -6397,7 +6403,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B136" s="15" t="s">
         <v>24</v>
@@ -6420,7 +6426,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="15" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B137" s="15" t="s">
         <v>25</v>
@@ -6443,7 +6449,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>111</v>
@@ -6469,12 +6475,12 @@
         <v>0.0275</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B140" s="15" t="s">
         <v>23</v>
@@ -6497,7 +6503,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B141" s="15" t="s">
         <v>24</v>
@@ -6520,7 +6526,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="15" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B142" s="15" t="s">
         <v>25</v>
@@ -6543,7 +6549,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>111</v>
@@ -6569,12 +6575,12 @@
         <v>0.6</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B145" s="15" t="s">
         <v>23</v>
@@ -6597,7 +6603,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B146" s="15" t="s">
         <v>24</v>
@@ -6620,7 +6626,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B147" s="15" t="s">
         <v>25</v>
@@ -6643,7 +6649,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>111</v>
@@ -6669,12 +6675,12 @@
         <v>4.75</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B150" s="15" t="s">
         <v>23</v>
@@ -6697,7 +6703,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B151" s="15" t="s">
         <v>24</v>
@@ -6720,7 +6726,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B152" s="15" t="s">
         <v>25</v>
@@ -6743,7 +6749,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>111</v>
@@ -6769,12 +6775,12 @@
         <v>6</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B155" s="15" t="s">
         <v>23</v>
@@ -6797,7 +6803,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B156" s="15" t="s">
         <v>24</v>
@@ -6820,7 +6826,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B157" s="15" t="s">
         <v>25</v>
@@ -6843,7 +6849,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="24" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B159" s="25"/>
       <c r="C159" s="25"/>
@@ -6855,10 +6861,10 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C160" s="17" t="n">
         <v>128.4</v>
@@ -6876,15 +6882,15 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B161" s="15" t="s">
         <v>206</v>
-      </c>
-      <c r="B161" s="15" t="s">
-        <v>204</v>
       </c>
       <c r="C161" s="17" t="n">
         <v>15.4</v>
@@ -6902,15 +6908,15 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C162" s="17" t="n">
         <v>34.5</v>
@@ -6928,15 +6934,15 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C163" s="17" t="n">
         <v>5.2</v>
@@ -6954,15 +6960,15 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C164" s="17" t="n">
         <v>89</v>
@@ -6980,15 +6986,15 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C165" s="17" t="n">
         <v>21.4</v>
@@ -7006,15 +7012,15 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C166" s="17" t="n">
         <v>21.9</v>
@@ -7032,15 +7038,15 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C167" s="17" t="n">
         <v>38.1</v>
@@ -7058,15 +7064,15 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C168" s="36" t="n">
         <f aca="false">C160+C165+C166+C167-C161-C162-C163-C164</f>
@@ -7089,25 +7095,25 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C172" s="31" t="n">
         <v>0</v>
@@ -7125,15 +7131,15 @@
         <v>1</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C174" s="17" t="n">
         <v>0</v>
@@ -7151,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -7180,43 +7186,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>1120.8</v>
@@ -7238,12 +7244,12 @@
         <v>1018.7</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>370.9</v>
@@ -7265,12 +7271,12 @@
         <v>417.4</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B7" s="38" t="n">
         <f aca="false">B5-B6</f>
@@ -7299,7 +7305,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B8" s="17" t="n">
         <v>341.3</v>
@@ -7321,12 +7327,12 @@
         <v>319.3</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>85.2</v>
@@ -7348,12 +7354,12 @@
         <v>20.2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B10" s="17" t="n">
         <v>99.4</v>
@@ -7375,12 +7381,12 @@
         <v>48.4</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B11" s="17" t="n">
         <v>2.5</v>
@@ -7402,12 +7408,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>0</v>
@@ -7429,12 +7435,12 @@
         <v>10.1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="37" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B13" s="38" t="n">
         <f aca="false">B7-B8-B9-B10-B11+B12</f>
@@ -7463,7 +7469,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>107</v>
@@ -7485,12 +7491,12 @@
         <v>96.7</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>-8.8</v>
@@ -7514,7 +7520,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B16" s="38" t="n">
         <f aca="false">B13-B14+B15</f>
@@ -7543,7 +7549,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B17" s="17" t="n">
         <v>35.3</v>
@@ -7565,12 +7571,12 @@
         <v>37.5</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B18" s="38" t="n">
         <f aca="false">B16-B17</f>
@@ -7599,7 +7605,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B19" s="17" t="n">
         <v>70.4</v>
@@ -7621,12 +7627,12 @@
         <v>87.5</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -7638,7 +7644,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B22" s="17" t="n">
         <v>32.6</v>
@@ -7660,12 +7666,12 @@
         <v>44.2</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>21.5</v>
@@ -7687,12 +7693,12 @@
         <v>25.3</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B24" s="38" t="n">
         <f aca="false">B13+B22+B10+B11-B12</f>
@@ -7721,7 +7727,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B25" s="39" t="n">
         <f aca="false">IFERROR(B24/B5,0)</f>
@@ -7750,7 +7756,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B26" s="27" t="n">
         <f aca="false">B24+B23</f>
@@ -7779,7 +7785,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D27" s="17" t="n">
         <v>415.3</v>
@@ -7795,43 +7801,43 @@
         <v>337.4</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B31" s="17" t="n">
         <v>601.4</v>
@@ -7853,12 +7859,12 @@
         <v>489.1</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B32" s="17" t="n">
         <v>519.4</v>
@@ -7880,12 +7886,12 @@
         <v>529.6</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B33" s="17" t="n">
         <v>0</v>
@@ -7907,12 +7913,12 @@
         <v>13.8</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B34" s="38" t="n">
         <f aca="false">B31+B32</f>
@@ -7941,7 +7947,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C35" s="39" t="n">
         <f aca="false">C31/B31-1</f>
@@ -7958,7 +7964,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B36" s="17" t="n">
         <v>829.2</v>
@@ -7980,12 +7986,12 @@
         <v>705.4</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B37" s="17" t="n">
         <v>138.1</v>
@@ -8009,7 +8015,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B38" s="17" t="n">
         <v>126.3</v>
@@ -8033,7 +8039,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B39" s="17" t="n">
         <v>14.2</v>
@@ -8057,7 +8063,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B40" s="17" t="n">
         <v>13</v>
@@ -8079,12 +8085,12 @@
         <v>17.1</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C41" s="39" t="n">
         <f aca="false">C36/B36-1</f>
@@ -8101,29 +8107,29 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B44" s="17" t="n">
         <v>326.5</v>
@@ -8138,12 +8144,12 @@
         <v>218.2</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B45" s="17" t="n">
         <v>16.7</v>
@@ -8158,12 +8164,12 @@
         <v>182.2</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B46" s="17" t="n">
         <v>152.1</v>
@@ -8180,7 +8186,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B47" s="17" t="n">
         <v>253.8</v>
@@ -8195,12 +8201,12 @@
         <v>90.5</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B48" s="38" t="n">
         <f aca="false">SUM(B44:B47)</f>
@@ -8223,7 +8229,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B49" s="17" t="n">
         <v>300.2</v>
@@ -8240,7 +8246,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B50" s="17" t="n">
         <v>24.7</v>
@@ -8255,12 +8261,12 @@
         <v>87.4</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B51" s="17" t="n">
         <v>140.4</v>
@@ -8277,7 +8283,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B52" s="38" t="n">
         <f aca="false">B48+B49+B50+B51</f>
@@ -8300,7 +8306,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B53" s="17" t="n">
         <v>1214.4</v>
@@ -8317,7 +8323,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B54" s="17" t="n">
         <v>53.5</v>
@@ -8334,7 +8340,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B55" s="17" t="n">
         <v>290.5</v>
@@ -8349,12 +8355,12 @@
         <v>189.9</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B56" s="17" t="n">
         <v>0</v>
@@ -8369,12 +8375,12 @@
         <v>129.9</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B57" s="17" t="n">
         <v>1603.4</v>
@@ -8389,12 +8395,12 @@
         <v>1325.2</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B58" s="17" t="n">
         <v>88.7</v>
@@ -8411,7 +8417,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="37" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B59" s="38" t="n">
         <f aca="false">SUM(B54:B58)</f>
@@ -8434,7 +8440,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B60" s="17" t="n">
         <v>-821.7</v>
@@ -8449,12 +8455,12 @@
         <v>-612.7</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B61" s="38" t="n">
         <f aca="false">B59+B60</f>
@@ -8477,33 +8483,33 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B64" s="36" t="n">
         <f aca="false">B18</f>
@@ -8532,7 +8538,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B65" s="36" t="n">
         <f aca="false">B22</f>
@@ -8561,7 +8567,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B66" s="17" t="n">
         <v>44.7</v>
@@ -8583,12 +8589,12 @@
         <v>53.6</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B67" s="17" t="n">
         <v>-63.9</v>
@@ -8610,12 +8616,12 @@
         <v>-10.5</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B68" s="17" t="n">
         <v>-16.1</v>
@@ -8639,7 +8645,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="37" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B69" s="38" t="n">
         <f aca="false">SUM(B64:B68)</f>
@@ -8668,7 +8674,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B70" s="17" t="n">
         <v>26.5</v>
@@ -8690,12 +8696,12 @@
         <v>9.5</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="37" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B71" s="38" t="n">
         <f aca="false">B69-B70</f>
@@ -8724,7 +8730,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B72" s="17" t="n">
         <v>0</v>
@@ -8748,7 +8754,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B73" s="17" t="n">
         <v>0</v>
@@ -8772,7 +8778,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B74" s="17" t="n">
         <v>-9.5</v>
@@ -8794,12 +8800,12 @@
         <v>-149.8</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B75" s="17" t="n">
         <v>0</v>
@@ -8821,12 +8827,12 @@
         <v>129.9</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B76" s="17" t="n">
         <v>-34.4</v>
@@ -8850,7 +8856,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B77" s="17" t="n">
         <v>0</v>
@@ -8874,7 +8880,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B78" s="17" t="n">
         <v>-4.8</v>
@@ -8898,7 +8904,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B79" s="17" t="n">
         <v>3.1</v>
@@ -8922,7 +8928,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="37" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B80" s="38" t="n">
         <f aca="false">B71+SUM(B72:B79)</f>
@@ -8951,7 +8957,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B81" s="17" t="n">
         <v>330.9</v>
@@ -8971,7 +8977,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="37" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B82" s="38" t="n">
         <f aca="false">B81+B80</f>
@@ -8997,7 +9003,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B83" s="17" t="n">
         <v>326.5</v>
@@ -9041,49 +9047,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>716.8</v>
@@ -9092,7 +9098,7 @@
         <v>639.4</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E5" s="41" t="n">
         <v>0.03</v>
@@ -9107,12 +9113,12 @@
         <v>2029</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>500</v>
@@ -9121,7 +9127,7 @@
         <v>500</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E6" s="41" t="n">
         <v>0.05</v>
@@ -9133,12 +9139,12 @@
         <v>2030</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>200</v>
@@ -9147,7 +9153,7 @@
         <v>200</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E7" s="41" t="n">
         <v>0.0675</v>
@@ -9159,15 +9165,15 @@
         <v>2030</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E8" s="41" t="n">
         <v>0.03</v>
@@ -9185,15 +9191,15 @@
         <v>100</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E9" s="41" t="n">
         <v>0.035</v>
@@ -9211,12 +9217,12 @@
         <v>210</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B10" s="17" t="n">
         <v>0</v>
@@ -9225,15 +9231,15 @@
         <v>129.9</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B11" s="38" t="n">
         <f aca="false">B5+B6+B7+B10</f>
@@ -9250,7 +9256,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>1416.8</v>
@@ -9259,12 +9265,12 @@
         <v>1469.3</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B13" s="17" t="n">
         <v>18.6</v>
@@ -9273,34 +9279,34 @@
         <v>14.2</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>500</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B15" s="17" t="n">
         <v>9.5</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B16" s="17" t="n">
         <v>1186.2</v>
@@ -9313,15 +9319,15 @@
         <v>0.815201704350217</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>103</v>
@@ -9341,7 +9347,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B19" s="31" t="n">
         <v>2025</v>
@@ -9369,7 +9375,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="25"/>
@@ -9380,7 +9386,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B21" s="36" t="n">
         <f aca="false">B14</f>
@@ -9407,12 +9413,12 @@
         <v>210</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
@@ -9423,7 +9429,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C23" s="9" t="n">
         <f aca="false">Model!C71</f>
@@ -9448,7 +9454,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C24" s="36" t="n">
         <f aca="false">-C36</f>
@@ -9473,7 +9479,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C25" s="36" t="n">
         <f aca="false">-(C37+C42+C46)*(1-Drivers!C$129)</f>
@@ -9498,7 +9504,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C26" s="36" t="n">
         <f aca="false">-C55</f>
@@ -9523,7 +9529,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="38" t="n">
@@ -9549,7 +9555,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C28" s="9" t="n">
         <f aca="false">Drivers!C$114</f>
@@ -9574,7 +9580,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C29" s="36" t="n">
         <f aca="false">C27-C28</f>
@@ -9599,7 +9605,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C30" s="36" t="n">
         <f aca="false">IF(C29&lt;0,MIN(-C29,C21-(C54-C55)),0)</f>
@@ -9624,7 +9630,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C31" s="36" t="n">
         <f aca="false">IF(C29&gt;0,MIN(C29,C54-C55),0)</f>
@@ -9649,7 +9655,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C32" s="36" t="n">
         <f aca="false">MAX(0,C29-C31)*Drivers!C$119</f>
@@ -9674,7 +9680,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C33" s="27" t="n">
         <f aca="false">MAX(0,-(C29+C30))</f>
@@ -9699,7 +9705,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="24" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
@@ -9710,7 +9716,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C35" s="36" t="n">
         <f aca="false">B39</f>
@@ -9735,7 +9741,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C36" s="36" t="n">
         <f aca="false">IF(C$19&lt;=$H$5,MIN(C35,$B$15),0)</f>
@@ -9760,7 +9766,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C37" s="36" t="n">
         <f aca="false">IF(C$19=$H$5,C35-C36,0)</f>
@@ -9785,7 +9791,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C38" s="36" t="n">
         <f aca="false">IF(C$19&lt;$H$5,MIN(C32,C35-C36),0)</f>
@@ -9810,7 +9816,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="37" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B39" s="44" t="n">
         <f aca="false">B5</f>
@@ -9839,7 +9845,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="24" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B40" s="25"/>
       <c r="C40" s="25"/>
@@ -9850,7 +9856,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C41" s="36" t="n">
         <f aca="false">B43</f>
@@ -9875,7 +9881,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C42" s="36" t="n">
         <f aca="false">IF(C$19=$H$6,C41,0)</f>
@@ -9900,7 +9906,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="37" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B43" s="44" t="n">
         <f aca="false">B6</f>
@@ -9929,7 +9935,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="24" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B44" s="25"/>
       <c r="C44" s="25"/>
@@ -9940,7 +9946,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C45" s="36" t="n">
         <f aca="false">B47</f>
@@ -9965,7 +9971,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C46" s="36" t="n">
         <f aca="false">IF(C$19=$H$7,C45,0)</f>
@@ -9990,7 +9996,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="37" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B47" s="44" t="n">
         <f aca="false">B7</f>
@@ -10019,7 +10025,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="24" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B48" s="25"/>
       <c r="C48" s="25"/>
@@ -10030,7 +10036,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C49" s="36" t="n">
         <f aca="false">B52</f>
@@ -10055,7 +10061,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C50" s="36" t="n">
         <f aca="false">(C37+C42+C46)*Drivers!C$129</f>
@@ -10080,7 +10086,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C51" s="36" t="n">
         <f aca="false">MIN(C32-C38,C49+C50)</f>
@@ -10105,7 +10111,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="37" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B52" s="44" t="n">
         <f aca="false">0</f>
@@ -10134,7 +10140,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="24" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -10145,7 +10151,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C54" s="36" t="n">
         <f aca="false">B56</f>
@@ -10170,7 +10176,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C55" s="36" t="n">
         <f aca="false">MAX(0,C54-C21)</f>
@@ -10195,7 +10201,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="37" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B56" s="44" t="n">
         <f aca="false">B10</f>
@@ -10224,7 +10230,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B57" s="36" t="n">
         <f aca="false">B14-B10</f>
@@ -10253,7 +10259,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="24" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
@@ -10264,7 +10270,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B59" s="36" t="n">
         <f aca="false">B11</f>
@@ -10293,7 +10299,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B60" s="36" t="n">
         <f aca="false">B5+B6+B7</f>
@@ -10322,7 +10328,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C61" s="36" t="n">
         <f aca="false">B63</f>
@@ -10347,7 +10353,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C62" s="36" t="n">
         <f aca="false">MIN(C61,Drivers!C$144)</f>
@@ -10372,7 +10378,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B63" s="36" t="n">
         <f aca="false">B13</f>
@@ -10401,7 +10407,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C64" s="36" t="n">
         <f aca="false">B59-C59</f>
@@ -10426,7 +10432,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="24" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -10437,7 +10443,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C66" s="11" t="n">
         <f aca="false">Drivers!C$124</f>
@@ -10462,7 +10468,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C67" s="36" t="n">
         <f aca="false">C35*(MAX(C66,$F$5)+$E$5)</f>
@@ -10487,7 +10493,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C68" s="36" t="n">
         <f aca="false">C41*$E$6</f>
@@ -10512,7 +10518,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C69" s="36" t="n">
         <f aca="false">C45*$E$7</f>
@@ -10537,7 +10543,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C70" s="36" t="n">
         <f aca="false">C49*Drivers!C$134</f>
@@ -10562,7 +10568,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C71" s="36" t="n">
         <f aca="false">C54*(MAX(C66,$F$9)+$E$9)</f>
@@ -10587,7 +10593,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B72" s="45" t="n">
         <v>0.00375</v>
@@ -10613,12 +10619,12 @@
         <v>0.7875</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="37" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B73" s="40"/>
       <c r="C73" s="38" t="n">
@@ -10644,7 +10650,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C74" s="36" t="n">
         <f aca="false">C62</f>
@@ -10669,7 +10675,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C75" s="36" t="n">
         <f aca="false">Model!B37*Drivers!C$139</f>
@@ -10694,7 +10700,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="37" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B76" s="40"/>
       <c r="C76" s="38" t="n">
@@ -10720,7 +10726,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C77" s="39" t="n">
         <f aca="false">IFERROR(C73/B59,0)</f>
@@ -10769,18 +10775,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>103</v>
@@ -10803,7 +10809,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -10815,7 +10821,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">Historicals!D31</f>
@@ -10842,12 +10848,12 @@
         <v>335.033341675226</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">C6/B6-1</f>
@@ -10872,7 +10878,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">Historicals!D32</f>
@@ -10901,7 +10907,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">Historicals!D33</f>
@@ -10930,7 +10936,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B10" s="38" t="n">
         <f aca="false">B6+B8+B9</f>
@@ -10959,7 +10965,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B11" s="39" t="n">
         <f aca="false">Historicals!D5/Historicals!C5-1</f>
@@ -10988,7 +10994,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B12" s="39" t="n">
         <f aca="false">B6/B10</f>
@@ -11017,7 +11023,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -11029,7 +11035,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">Historicals!D5</f>
@@ -11058,7 +11064,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">Historicals!D6</f>
@@ -11087,7 +11093,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B16" s="38" t="n">
         <f aca="false">B14-B15</f>
@@ -11116,7 +11122,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">B16/B14</f>
@@ -11145,7 +11151,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">Historicals!D8</f>
@@ -11174,7 +11180,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">Historicals!D9</f>
@@ -11203,7 +11209,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B20" s="36" t="n">
         <f aca="false">Historicals!D10+Historicals!D11</f>
@@ -11232,7 +11238,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">Historicals!D12</f>
@@ -11261,7 +11267,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B22" s="38" t="n">
         <f aca="false">B16-B18-B19-B20+B21</f>
@@ -11290,7 +11296,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B23" s="9" t="n">
         <f aca="false">Historicals!D14</f>
@@ -11317,12 +11323,12 @@
         <v>57.5076206219581</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B24" s="9" t="n">
         <f aca="false">Historicals!D15</f>
@@ -11351,7 +11357,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="37" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B25" s="38" t="n">
         <f aca="false">B22-B23+B24</f>
@@ -11380,7 +11386,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B26" s="9" t="n">
         <f aca="false">Historicals!D17</f>
@@ -11409,7 +11415,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B27" s="38" t="n">
         <f aca="false">B25-B26</f>
@@ -11438,7 +11444,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
@@ -11450,7 +11456,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B29" s="9" t="n">
         <f aca="false">Historicals!D22</f>
@@ -11479,7 +11485,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C30" s="9" t="n">
         <f aca="false">Drivers!C$62</f>
@@ -11504,7 +11510,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C31" s="36" t="n">
         <f aca="false">C29-C30</f>
@@ -11529,7 +11535,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B32" s="38" t="n">
         <f aca="false">B22+B29+B20-B21</f>
@@ -11556,12 +11562,12 @@
         <v>279.002534175109</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B33" s="39" t="n">
         <f aca="false">B32/B14</f>
@@ -11590,7 +11596,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B34" s="9" t="n">
         <f aca="false">Historicals!D23</f>
@@ -11619,7 +11625,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B35" s="27" t="n">
         <f aca="false">B32+B34</f>
@@ -11648,7 +11654,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
@@ -11660,7 +11666,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B37" s="9" t="n">
         <f aca="false">Historicals!D44</f>
@@ -11689,7 +11695,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B38" s="9" t="n">
         <f aca="false">Historicals!D45</f>
@@ -11718,7 +11724,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B39" s="9" t="n">
         <f aca="false">Historicals!D46</f>
@@ -11747,7 +11753,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B40" s="9" t="n">
         <f aca="false">Historicals!D47</f>
@@ -11776,7 +11782,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B41" s="38" t="n">
         <f aca="false">SUM(B37:B40)</f>
@@ -11805,7 +11811,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B42" s="9" t="n">
         <f aca="false">Historicals!D49</f>
@@ -11834,7 +11840,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B43" s="9" t="n">
         <f aca="false">Historicals!D50</f>
@@ -11863,7 +11869,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B44" s="9" t="n">
         <f aca="false">Historicals!D51</f>
@@ -11890,12 +11896,12 @@
         <v>179.9</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B45" s="38" t="n">
         <f aca="false">B41+B42+B43+B44</f>
@@ -11924,7 +11930,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B46" s="9" t="n">
         <f aca="false">Historicals!D54</f>
@@ -11953,7 +11959,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B47" s="9" t="n">
         <f aca="false">Historicals!D55</f>
@@ -11980,12 +11986,12 @@
         <v>199.2</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B48" s="9" t="n">
         <f aca="false">Historicals!D56</f>
@@ -12014,7 +12020,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B49" s="9" t="n">
         <f aca="false">Historicals!D57</f>
@@ -12043,7 +12049,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B50" s="9" t="n">
         <f aca="false">Historicals!D58</f>
@@ -12072,7 +12078,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="37" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B51" s="38" t="n">
         <f aca="false">SUM(B46:B50)</f>
@@ -12101,7 +12107,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B52" s="9" t="n">
         <f aca="false">Historicals!D60</f>
@@ -12128,12 +12134,12 @@
         <v>-51.6934919923408</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B53" s="38" t="n">
         <f aca="false">B51+B52</f>
@@ -12162,7 +12168,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="24" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="25"/>
@@ -12174,7 +12180,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C55" s="36" t="n">
         <f aca="false">C27</f>
@@ -12199,7 +12205,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C56" s="36" t="n">
         <f aca="false">C29</f>
@@ -12224,7 +12230,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C57" s="36" t="n">
         <f aca="false">C34</f>
@@ -12249,7 +12255,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C58" s="9" t="n">
         <f aca="false">Debt!C74</f>
@@ -12274,7 +12280,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C59" s="36" t="n">
         <f aca="false">-C21</f>
@@ -12299,7 +12305,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C60" s="36" t="n">
         <f aca="false">-(C38-B38-Drivers!C$161)</f>
@@ -12324,7 +12330,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C61" s="36" t="n">
         <f aca="false">-(C39-B39-Drivers!C$162)</f>
@@ -12349,7 +12355,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C62" s="36" t="n">
         <f aca="false">C46-B46</f>
@@ -12374,7 +12380,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="37" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B63" s="46" t="n">
         <f aca="false">Historicals!D69</f>
@@ -12403,7 +12409,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B64" s="9" t="n">
         <f aca="false">Historicals!D70</f>
@@ -12432,7 +12438,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="37" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B65" s="38" t="n">
         <f aca="false">B63-B64</f>
@@ -12461,7 +12467,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C66" s="9" t="n">
         <f aca="false">-Drivers!C$160</f>
@@ -12486,7 +12492,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C67" s="9" t="n">
         <f aca="false">Drivers!C$52</f>
@@ -12511,7 +12517,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C68" s="9" t="n">
         <f aca="false">-Drivers!C$99</f>
@@ -12536,7 +12542,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C69" s="9" t="n">
         <f aca="false">-Drivers!C$104</f>
@@ -12561,7 +12567,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C70" s="9" t="n">
         <f aca="false">-Drivers!C$109</f>
@@ -12586,7 +12592,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C71" s="36" t="n">
         <f aca="false">B37+C65+SUM(C66:C70)</f>
@@ -12609,12 +12615,12 @@
         <v>355.052378856658</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C72" s="9" t="n">
         <f aca="false">-Debt!C36</f>
@@ -12639,7 +12645,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C73" s="36" t="n">
         <f aca="false">-(Debt!C37+Debt!C42+Debt!C46)</f>
@@ -12664,7 +12670,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C74" s="9" t="n">
         <f aca="false">Debt!C50</f>
@@ -12689,7 +12695,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C75" s="36" t="n">
         <f aca="false">Debt!C30-Debt!C31-Debt!C55</f>
@@ -12714,7 +12720,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C76" s="36" t="n">
         <f aca="false">-(Debt!C38+Debt!C51)</f>
@@ -12739,7 +12745,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="37" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B77" s="40"/>
       <c r="C77" s="38" t="n">
@@ -12765,7 +12771,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C78" s="36" t="n">
         <f aca="false">B37</f>
@@ -12790,7 +12796,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="37" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B79" s="46" t="n">
         <f aca="false">Historicals!D44</f>
@@ -12819,7 +12825,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -12849,20 +12855,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>103</v>
@@ -12888,7 +12894,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -12901,7 +12907,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">Model!B32</f>
@@ -12934,7 +12940,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">Model!B35</f>
@@ -12967,7 +12973,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">Debt!B59</f>
@@ -12998,12 +13004,12 @@
         <v>1469.3</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">Model!B37</f>
@@ -13036,7 +13042,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">B8-B9</f>
@@ -13069,7 +13075,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">Historicals!D14</f>
@@ -13102,7 +13108,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">Model!B64</f>
@@ -13135,7 +13141,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">Model!B65</f>
@@ -13168,7 +13174,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">Debt!B57</f>
@@ -13199,12 +13205,12 @@
         <v>180.1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -13217,7 +13223,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B16" s="47" t="n">
         <f aca="false">IFERROR(B8/B6,0)</f>
@@ -13250,7 +13256,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B17" s="48" t="n">
         <f aca="false">IFERROR(B10/B6,0)</f>
@@ -13283,7 +13289,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B18" s="47" t="n">
         <f aca="false">B17</f>
@@ -13314,12 +13320,12 @@
         <v>4.08856209150327</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B19" s="47" t="n">
         <f aca="false">IFERROR(B10/B7,0)</f>
@@ -13350,12 +13356,12 @@
         <v>3.77633564744944</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">Drivers!C$149</f>
@@ -13380,7 +13386,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C21" s="39" t="n">
         <f aca="false">IFERROR(1-(C10/C20)/C7,0)</f>
@@ -13403,12 +13409,12 @@
         <v>0.577191698054959</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C22" s="36" t="n">
         <f aca="false">C10/C20</f>
@@ -13433,7 +13439,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -13446,7 +13452,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B24" s="48" t="n">
         <f aca="false">IFERROR(B6/B11,0)</f>
@@ -13479,7 +13485,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B25" s="47" t="n">
         <f aca="false">IFERROR((B6-B12)/B11,0)</f>
@@ -13512,7 +13518,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B26" s="39" t="n">
         <f aca="false">IFERROR(B13/B8,0)</f>
@@ -13545,7 +13551,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C27" s="36" t="n">
         <f aca="false">Debt!$B$59-C8</f>
@@ -13570,7 +13576,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B28" s="25"/>
       <c r="C28" s="25"/>
@@ -13583,7 +13589,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B29" s="27" t="n">
         <f aca="false">B9+B14</f>
@@ -13616,7 +13622,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C30" s="36" t="n">
         <f aca="false">Debt!C36+Debt!C37+Debt!C42+Debt!C46+Debt!C55</f>
@@ -13641,7 +13647,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C31" s="36" t="n">
         <f aca="false">SUM(D30:E30)</f>
@@ -13664,12 +13670,12 @@
         <v>0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C32" s="47" t="n">
         <f aca="false">IFERROR(C29/C31,0)</f>
@@ -13694,7 +13700,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C33" s="49" t="n">
         <f aca="false">Debt!C33</f>
@@ -13719,7 +13725,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="24" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="25"/>
@@ -13732,7 +13738,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C35" s="36" t="n">
         <f aca="false">C6*Drivers!C$154</f>
@@ -13757,7 +13763,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C36" s="39" t="n">
         <f aca="false">IFERROR(MIN(1,C35/C10),0)</f>
@@ -13780,12 +13786,12 @@
         <v>1</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C37" s="3" t="str">
         <f aca="false">IF(Model!C37&lt;0,"DEFAULT",IF(C19&gt;C20,"COVENANT BREACH","OK"))</f>
@@ -13810,7 +13816,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="24" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -13958,7 +13964,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="24" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B56" s="25"/>
       <c r="C56" s="25"/>
@@ -13971,18 +13977,18 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B57" s="29" t="n">
         <v>81</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B58" s="50" t="n">
         <v>46318</v>
@@ -13990,7 +13996,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B59" s="51" t="n">
         <f aca="false">Debt!G6</f>
@@ -13999,7 +14005,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B60" s="12" t="n">
         <f aca="false">Debt!E6</f>
@@ -14008,7 +14014,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B61" s="52" t="n">
         <f aca="false">YIELD(B58,B59,B60,B57,100,2,0)</f>
@@ -14017,7 +14023,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B62" s="52" t="n">
         <f aca="false">B60*100/B57</f>
@@ -14026,19 +14032,19 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B63" s="53" t="n">
         <f aca="false">B53*100-B57</f>
         <v>19</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="24" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -14051,27 +14057,27 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C67" s="17" t="n">
         <v>2.4</v>
@@ -14089,12 +14095,12 @@
         <v>700</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C68" s="36" t="n">
         <f aca="false">C30</f>
@@ -14119,7 +14125,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -14149,15 +14155,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>103</v>
@@ -14175,12 +14181,12 @@
         <v>107</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B5" s="54" t="n">
         <f aca="false">Model!B45-Model!B53</f>
@@ -14207,12 +14213,12 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B6" s="3" t="str">
         <f aca="false">IF(ABS(B5)&lt;0.05,"OK","FAIL")</f>
@@ -14241,7 +14247,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B7" s="54" t="n">
         <f aca="false">Model!B79-Model!B37</f>
@@ -14271,7 +14277,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B8" s="3" t="str">
         <f aca="false">IF(ABS(B7)&lt;0.05,"OK","FAIL")</f>
@@ -14300,7 +14306,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B9" s="54" t="n">
         <f aca="false">Debt!B59-Debt!B63-Model!B48-Model!B49</f>
@@ -14330,7 +14336,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B10" s="3" t="str">
         <f aca="false">IF(ABS(B9)&lt;0.05,"OK","FAIL")</f>
@@ -14359,7 +14365,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C11" s="54" t="n">
         <f aca="false">Debt!C27+Debt!C30-Debt!C31-Debt!C38-Debt!C51-Model!C37</f>
@@ -14382,12 +14388,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C12" s="3" t="str">
         <f aca="false">IF(ABS(C11)&lt;0.05,"OK","FAIL")</f>
@@ -14412,7 +14418,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C13" s="54" t="n">
         <f aca="false">MAX(0,Debt!C56-Debt!C21)</f>
@@ -14438,7 +14444,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C14" s="3" t="str">
         <f aca="false">IF(ABS(C13)&lt;0.05,"OK","FAIL")</f>
@@ -14463,7 +14469,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C15" s="54" t="n">
         <f aca="false">Model!C10-Model!C14</f>
@@ -14489,7 +14495,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C16" s="3" t="str">
         <f aca="false">IF(ABS(C15)&lt;0.05,"OK","FAIL")</f>
@@ -14514,7 +14520,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B17" s="54" t="n">
         <f aca="false">Debt!B11-Debt!B12</f>
@@ -14524,7 +14530,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B18" s="3" t="str">
         <f aca="false">IF(ABS(B17)&lt;0.05,"OK","FAIL")</f>
@@ -14533,7 +14539,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B19" s="54" t="n">
         <f aca="false">Debt!C11-Debt!C12</f>
@@ -14543,7 +14549,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B20" s="3" t="str">
         <f aca="false">IF(ABS(B19)&lt;0.05,"OK","FAIL")</f>
@@ -14552,7 +14558,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
@@ -14565,26 +14571,26 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B24" s="54" t="n">
         <f aca="false">Historicals!B18-Historicals!B19</f>
@@ -14607,12 +14613,12 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B25" s="3" t="str">
         <f aca="false">IF(ABS(B24)&lt;0.05,"OK","FAIL")</f>
@@ -14637,7 +14643,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B26" s="54" t="n">
         <f aca="false">Historicals!B52-Historicals!B53</f>
@@ -14659,7 +14665,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B27" s="3" t="str">
         <f aca="false">IF(ABS(B26)&lt;0.05,"OK","FAIL")</f>
@@ -14680,7 +14686,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B28" s="54" t="n">
         <f aca="false">Historicals!B52-Historicals!B61</f>
@@ -14702,7 +14708,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B29" s="3" t="str">
         <f aca="false">IF(ABS(B28)&lt;0.05,"OK","FAIL")</f>
@@ -14723,7 +14729,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B30" s="54" t="n">
         <f aca="false">Historicals!B82-Historicals!B83</f>
@@ -14746,12 +14752,12 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B31" s="3" t="str">
         <f aca="false">IF(ABS(B30)&lt;0.05,"OK","FAIL")</f>
@@ -14776,7 +14782,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B32" s="54" t="n">
         <f aca="false">Historicals!B34-Historicals!B5</f>
@@ -14802,7 +14808,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B33" s="3" t="str">
         <f aca="false">IF(ABS(B32)&lt;0.05,"OK","FAIL")</f>
@@ -14827,7 +14833,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B34" s="54" t="n">
         <f aca="false">SUM(Historicals!B36:B40)-Historicals!B5</f>
@@ -14853,7 +14859,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B35" s="3" t="str">
         <f aca="false">IF(ABS(B34)&lt;0.05,"OK","FAIL")</f>
@@ -14878,7 +14884,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="24" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -14890,7 +14896,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B38" s="17" t="n">
         <v>1015</v>
@@ -14903,12 +14909,12 @@
         <v>OK</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C39" s="3" t="str">
         <f aca="false">IF(Model!C37&gt;=0,"OK","DEFAULT")</f>
@@ -14933,18 +14939,18 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="55" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B42" s="55" t="str">
         <f aca="false">IF(SUMPRODUCT(--((B6:G6)="FAIL"))+SUMPRODUCT(--((B8:G8)="FAIL"))+SUMPRODUCT(--((B10:G10)="FAIL"))+SUMPRODUCT(--((B12:G12)="FAIL"))+SUMPRODUCT(--((B14:G14)="FAIL"))+SUMPRODUCT(--((B16:G16)="FAIL"))+SUMPRODUCT(--((B18:G18)="FAIL"))+SUMPRODUCT(--((B20:G20)="FAIL"))+SUMPRODUCT(--((B25:G25)="FAIL"))+SUMPRODUCT(--((B27:G27)="FAIL"))+SUMPRODUCT(--((B29:G29)="FAIL"))+SUMPRODUCT(--((B31:G31)="FAIL"))+SUMPRODUCT(--((B33:G33)="FAIL"))+SUMPRODUCT(--((B35:G35)="FAIL"))=0,"ALL CHECKS OK","FAIL")</f>
